--- a/426-config---paramètre-pin-all/ig/ValueSet-tddui-goal-objectif-note-vs.xlsx
+++ b/426-config---paramètre-pin-all/ig/ValueSet-tddui-goal-objectif-note-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T15:49:47+00:00</t>
+    <t>2026-01-30T16:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,7 +103,7 @@
     <t>ValueSet URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-discriminator-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-discriminator-vs</t>
   </si>
   <si>
     <t>Concept</t>
